--- a/week-1/data-gathering-tables.xlsx
+++ b/week-1/data-gathering-tables.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vernwolfley/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vernwolfley/Documents/byui_education/ITM-111/itm111-introduction-to-databases/week-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBF0FD4-86DE-974E-9F19-68F3B32F9A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB2AB67-AECD-AF47-B0D5-D0BDFB6C02F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="25680" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -146,7 +146,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -260,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -271,14 +271,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -288,17 +284,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,15 +539,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -577,34 +576,56 @@
       <c r="A3" s="6">
         <v>46281</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
+      <c r="B3" s="14">
+        <v>5</v>
+      </c>
+      <c r="C3" s="14">
+        <v>3</v>
+      </c>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14">
+        <v>4</v>
+      </c>
+      <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>46282</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="14">
+        <v>2</v>
+      </c>
+      <c r="C4" s="14">
+        <v>3</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14">
+        <v>1</v>
+      </c>
+      <c r="F4" s="14">
+        <v>4</v>
+      </c>
+      <c r="G4" s="14"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>46283</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="B5" s="14">
+        <v>3</v>
+      </c>
+      <c r="C5" s="14">
+        <v>2</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14">
+        <v>2</v>
+      </c>
+      <c r="F5" s="14">
+        <v>4</v>
+      </c>
+      <c r="G5" s="14"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8"/>
@@ -851,8 +872,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.5" style="3" bestFit="1" customWidth="1"/>
@@ -868,17 +889,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -886,243 +907,243 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="11" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>24</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="11" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="11" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="11"/>
+      <c r="C13" s="9"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="11"/>
+      <c r="C14" s="9"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="11"/>
+      <c r="C15" s="9"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="11"/>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="11"/>
+      <c r="C17" s="9"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="11"/>
+      <c r="C18" s="9"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19"/>
       <c r="B19" s="1"/>
-      <c r="C19" s="11"/>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="11"/>
+      <c r="C20" s="9"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="11"/>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="11"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="11"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="11"/>
+      <c r="C24" s="9"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="11"/>
+      <c r="C25" s="9"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="11"/>
+      <c r="C26" s="9"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="11"/>
+      <c r="C27" s="9"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="11"/>
+      <c r="C28" s="9"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="11"/>
+      <c r="C29" s="9"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30"/>
       <c r="B30" s="1"/>
-      <c r="C30" s="11"/>
+      <c r="C30" s="9"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31"/>
       <c r="B31" s="1"/>
-      <c r="C31" s="11"/>
+      <c r="C31" s="9"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="11"/>
+      <c r="C32" s="9"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33"/>
       <c r="B33" s="1"/>
-      <c r="C33" s="11"/>
+      <c r="C33" s="9"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34"/>
       <c r="B34" s="1"/>
-      <c r="C34" s="11"/>
+      <c r="C34" s="9"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35"/>
       <c r="B35" s="1"/>
-      <c r="C35" s="11"/>
+      <c r="C35" s="9"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="11"/>
+      <c r="C36" s="9"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="11"/>
+      <c r="C37" s="9"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="11"/>
+      <c r="C38" s="9"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="11"/>
+      <c r="C39" s="9"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="11"/>
+      <c r="C40" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1167,12 +1188,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
@@ -1189,282 +1210,282 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="17">
+      <c r="A3" s="13">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="17">
+      <c r="A4" s="13">
         <v>2</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="17">
+      <c r="A5" s="13">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="17">
+      <c r="A6" s="13">
         <v>4</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="17">
+      <c r="A7" s="13">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="17">
+      <c r="A8" s="13">
         <v>6</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="17">
+      <c r="A9" s="13">
         <v>7</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="14">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="17">
+      <c r="A10" s="13">
         <v>8</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="17">
+      <c r="A11" s="13">
         <v>9</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="17">
+      <c r="A12" s="13">
         <v>10</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="17">
+      <c r="A13" s="13">
         <v>11</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="14">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="17">
+      <c r="A14" s="13">
         <v>12</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="17">
+      <c r="A15" s="13">
         <v>13</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="17">
+      <c r="A16" s="13">
         <v>14</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="17">
+      <c r="A17" s="13">
         <v>15</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="17">
+      <c r="A18" s="13">
         <v>16</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="14">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="17">
+      <c r="A19" s="13">
         <v>17</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="14">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="17">
+      <c r="A20" s="13">
         <v>18</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="14">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="17">
+      <c r="A21" s="13">
         <v>19</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="17">
+      <c r="A22" s="13">
         <v>20</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="14">
         <v>19</v>
       </c>
     </row>
